--- a/artifacts/aura-forecast/public/exports/MONTHLY_FORECAST_2026.csv.xlsx
+++ b/artifacts/aura-forecast/public/exports/MONTHLY_FORECAST_2026.csv.xlsx
@@ -3,6 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Monthly_Forecast" sheetId="1" r:id="rId1"/>
+    <sheet name="Analysis_Stats" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -77,27 +78,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.2513</t>
+          <t>26.2418</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4058</t>
+          <t>66.5113</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>969.8433</t>
+          <t>969.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0928</t>
+          <t>25.0688</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>327.6878</t>
+          <t>327.6332</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -114,27 +115,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26.2513</t>
+          <t>26.2275</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>66.4058</t>
+          <t>66.7922</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>969.8433</t>
+          <t>969.8656</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0928</t>
+          <t>25.087</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>327.6878</t>
+          <t>328.2276</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -151,27 +152,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26.2513</t>
+          <t>26.2478</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>66.4058</t>
+          <t>66.7181</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>969.8433</t>
+          <t>969.8753</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0928</t>
+          <t>25.0899</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>327.6878</t>
+          <t>328.0229</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -188,32 +189,219 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.2513</t>
+          <t>26.2292</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>66.4058</t>
+          <t>66.7119</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>969.8433</t>
+          <t>969.8627</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0928</t>
+          <t>25.0723</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>327.6878</t>
+          <t>327.9847</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>744</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Analysis item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Forecast rows in package</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Forecast profile</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>weekday × hour training profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Forecast target</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>refractivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Visual asset</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>analytics/data_quality_missingness.svg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Missing percentage by variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>analytics/data_quality_outliers.svg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Flagged outlier counts by variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>analytics/hist_temperature.svg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Temperature histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>analytics/hist_pressure.svg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pressure histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>analytics/hist_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Refractivity histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>analytics/correlation_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Predictor correlation with refractivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>analytics/daily_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Daily refractivity trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>analytics/monthly_forecast.svg</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Monthly forecast comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>analytics/validation_metrics.svg</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chronological validation scorecard</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>analytics/training_holdout_rows.svg</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Training, holdout, and validation counts</t>
         </is>
       </c>
     </row>

--- a/artifacts/aura-forecast/public/exports/MONTHLY_FORECAST_2026.csv.xlsx
+++ b/artifacts/aura-forecast/public/exports/MONTHLY_FORECAST_2026.csv.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>327.6332</t>
+          <t>345.2927</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>328.2276</t>
+          <t>345.6343</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -172,7 +172,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>328.0229</t>
+          <t>345.5977</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -209,7 +209,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>327.9847</t>
+          <t>345.5466</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
